--- a/results/BDDTestGen Participant Questionnaire (answers).xlsx
+++ b/results/BDDTestGen Participant Questionnaire (answers).xlsx
@@ -1,119 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Respostas ao formulário 1" sheetId="1" r:id="rId4"/>
+    <sheet name="Respostas ao formulário 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
-  <si>
-    <t>Carimbo de data/hora</t>
-  </si>
-  <si>
-    <t>Do you confirm your participation in the research, knowing that you meet the profile and understand the objectives, risks and benefits involved?</t>
-  </si>
-  <si>
-    <t>What is your level of experience in software development?</t>
-  </si>
-  <si>
-    <t>Describe the other option briefly</t>
-  </si>
-  <si>
-    <t>What is your level of experience with BDD (Behavior-Driven Development)?</t>
-  </si>
-  <si>
-    <t>What is your level of experience with test automation?</t>
-  </si>
-  <si>
-    <t>1. How do you rate the learning curve to be able to use the tool properly?</t>
-  </si>
-  <si>
-    <t>2. How do you rate the difficulty in completing the task with the tool, compared to manually executing it?</t>
-  </si>
-  <si>
-    <t>3. How do you rate the time required to generate the scenarios and test data with the tool, compared to manually writing it?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Did you notice any errors while running the tool (e.g., crashes, freezes, unexpected behaviors)? </t>
-  </si>
-  <si>
-    <t>4.1. If the answer to the previous question was "Yes", explain briefly what issues you ran into.</t>
-  </si>
-  <si>
-    <t>5.  Did you notice any errors in the results generated by the tool (e.g., inconsistent scenarios, inadequate data, incorrect structure)?</t>
-  </si>
-  <si>
-    <t>5.1.  If the answer to the previous question was "Yes", explain briefly what issues you ran into.</t>
-  </si>
-  <si>
-    <t>6- Leave your general feedback or observations about your experience with the tool. (Optional)</t>
-  </si>
-  <si>
-    <t>Agree</t>
-  </si>
-  <si>
-    <t>I have been working professionally in a company or academic institution for 1 to 3 years</t>
-  </si>
-  <si>
-    <t>I have used BDD in personal or extracurricular projects</t>
-  </si>
-  <si>
-    <t>I use it in a professional context (company or research institution)</t>
-  </si>
-  <si>
-    <t>Very easy</t>
-  </si>
-  <si>
-    <t>Very fast</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>O plugin é bastante prático e rápido de configurar, caso seja necessário configurá-lo novamente, isso não será um problema. Durante a execução da ferramenta, não identifiquei nenhum problema. O arquivo .feature gerado é bem estruturado e reflete bem o que foi solicitado. Não testei com exemplos mais complexos porém em alguns casos pode ser necessário realizar pequenas modificações no .feature gerado (normal quando se utiliza LLMs). De qualquer forma, ter uma ferramenta que automatiza parte desse processo é de grande ajuda.</t>
-  </si>
-  <si>
-    <t>I have been working professionally in a company or academic institution for more than 3 year</t>
-  </si>
-  <si>
-    <t>I use BDD in a professional context (company or research institution)</t>
-  </si>
-  <si>
-    <t>Fast</t>
-  </si>
-  <si>
-    <t>I've really enjoyed using the tool. As a suggestion for improvement, it would be great to add a distinct icon or symbol to make it stand out among the available options. Alternatively, you could consider adopting an approach similar to VSCode, where extensions are displayed in a clearly visible sidebar.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -249,54 +166,55 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
       <font/>
       <fill>
-        <patternFill patternType="none"/>
+        <patternFill/>
       </fill>
       <border/>
     </dxf>
@@ -331,46 +249,105 @@
       <border/>
     </dxf>
   </dxfs>
-  <tableStyles count="1">
-    <tableStyle count="3" pivot="0" name="Respostas ao formulário 1-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Respostas ao formulário 1-style" pivot="0" count="3">
+      <tableStyleElement type="headerRow" dxfId="1"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="3"/>
     </tableStyle>
   </tableStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:P3" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses1" displayName="Form_Responses1" ref="A1:P3" headerRowCount="0">
   <tableColumns count="16">
-    <tableColumn name="Column1" id="1"/>
-    <tableColumn name="Column2" id="2"/>
-    <tableColumn name="Column3" id="3"/>
-    <tableColumn name="Column4" id="4"/>
-    <tableColumn name="Column5" id="5"/>
-    <tableColumn name="Column6" id="6"/>
-    <tableColumn name="Column7" id="7"/>
-    <tableColumn name="Column8" id="8"/>
-    <tableColumn name="Column9" id="9"/>
-    <tableColumn name="Column10" id="10"/>
-    <tableColumn name="Column11" id="11"/>
-    <tableColumn name="Column12" id="12"/>
-    <tableColumn name="Column13" id="13"/>
-    <tableColumn name="Column14" id="14"/>
-    <tableColumn name="Column15" id="15"/>
-    <tableColumn name="Column16" id="16"/>
+    <tableColumn id="1" name="Column1"/>
+    <tableColumn id="2" name="Column2"/>
+    <tableColumn id="3" name="Column3"/>
+    <tableColumn id="4" name="Column4"/>
+    <tableColumn id="5" name="Column5"/>
+    <tableColumn id="6" name="Column6"/>
+    <tableColumn id="7" name="Column7"/>
+    <tableColumn id="8" name="Column8"/>
+    <tableColumn id="9" name="Column9"/>
+    <tableColumn id="10" name="Column10"/>
+    <tableColumn id="11" name="Column11"/>
+    <tableColumn id="12" name="Column12"/>
+    <tableColumn id="13" name="Column13"/>
+    <tableColumn id="14" name="Column14"/>
+    <tableColumn id="15" name="Column15"/>
+    <tableColumn id="16" name="Column16"/>
   </tableColumns>
-  <tableStyleInfo name="Respostas ao formulário 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" headerRowCount="1"/>
-    </ext>
-  </extLst>
+  <tableStyleInfo name="Respostas ao formulário 1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -569,157 +546,231 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:P3"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="21.25"/>
-    <col customWidth="1" min="2" max="3" width="37.63"/>
-    <col customWidth="1" min="4" max="4" width="28.5"/>
-    <col customWidth="1" min="5" max="5" width="37.63"/>
-    <col customWidth="1" min="6" max="6" width="28.5"/>
-    <col customWidth="1" min="7" max="7" width="37.63"/>
-    <col customWidth="1" min="8" max="8" width="28.5"/>
-    <col customWidth="1" min="9" max="16" width="37.63"/>
-    <col customWidth="1" min="17" max="22" width="18.88"/>
+    <col width="21.25" customWidth="1" style="12" min="1" max="1"/>
+    <col width="37.63" customWidth="1" style="12" min="2" max="3"/>
+    <col width="28.5" customWidth="1" style="12" min="4" max="4"/>
+    <col width="37.63" customWidth="1" style="12" min="5" max="5"/>
+    <col width="28.5" customWidth="1" style="12" min="6" max="6"/>
+    <col width="37.63" customWidth="1" style="12" min="7" max="7"/>
+    <col width="28.5" customWidth="1" style="12" min="8" max="8"/>
+    <col width="37.63" customWidth="1" style="12" min="9" max="16"/>
+    <col width="18.88" customWidth="1" style="12" min="17" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>13</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Carimbo de data/hora</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Do you confirm your participation in the research, knowing that you meet the profile and understand the objectives, risks and benefits involved?</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>What is your level of experience in software development?</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Describe the other option briefly</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>What is your level of experience with BDD (Behavior-Driven Development)?</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Describe the other option briefly</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>What is your level of experience with test automation?</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Describe the other option briefly</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>1. How do you rate the learning curve to be able to use the tool properly?</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>2. How do you rate the difficulty in completing the task with the tool, compared to manually executing it?</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>3. How do you rate the time required to generate the scenarios and test data with the tool, compared to manually writing it?</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Did you notice any errors while running the tool (e.g., crashes, freezes, unexpected behaviors)? </t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>4.1. If the answer to the previous question was "Yes", explain briefly what issues you ran into.</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>5.  Did you notice any errors in the results generated by the tool (e.g., inconsistent scenarios, inadequate data, incorrect structure)?</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>5.1.  If the answer to the previous question was "Yes", explain briefly what issues you ran into.</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>6- Leave your general feedback or observations about your experience with the tool. (Optional)</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4">
-        <v>45799.66057378473</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="6"/>
-      <c r="I2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="6"/>
-      <c r="N2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="O2" s="6"/>
-      <c r="P2" s="7" t="s">
-        <v>21</v>
+      <c r="A2" s="4" t="n">
+        <v>45799.66057378472</v>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Agree</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>I have been working professionally in a company or academic institution for 1 to 3 years</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>I have used BDD in personal or extracurricular projects</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>I use it in a professional context (company or research institution)</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="n"/>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>Very fast</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M2" s="6" t="n"/>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O2" s="6" t="n"/>
+      <c r="P2" s="7" t="inlineStr">
+        <is>
+          <t>O plugin é bastante prático e rápido de configurar, caso seja necessário configurá-lo novamente, isso não será um problema. Durante a execução da ferramenta, não identifiquei nenhum problema. O arquivo .feature gerado é bem estruturado e reflete bem o que foi solicitado. Não testei com exemplos mais complexos porém em alguns casos pode ser necessário realizar pequenas modificações no .feature gerado (normal quando se utiliza LLMs). De qualquer forma, ter uma ferramenta que automatiza parte desse processo é de grande ajuda.</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8">
+      <c r="A3" s="8" t="n">
         <v>45799.71449261574</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="10"/>
-      <c r="I3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" s="10"/>
-      <c r="N3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="O3" s="10"/>
-      <c r="P3" s="11" t="s">
-        <v>25</v>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Agree</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>I have been working professionally in a company or academic institution for more than 3 year</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>I use BDD in a professional context (company or research institution)</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>I use it in a professional context (company or research institution)</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>Fast</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="11" t="inlineStr">
+        <is>
+          <t>I've really enjoyed using the tool. As a suggestion for improvement, it would be great to add a distinct icon or symbol to make it stand out among the available options. Alternatively, you could consider adopting an approach similar to VSCode, where extensions are displayed in a clearly visible sidebar.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>